--- a/sources/wang_step6b.xlsx
+++ b/sources/wang_step6b.xlsx
@@ -422,7 +422,7 @@
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="7" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
@@ -2413,7 +2413,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>G-Clef - Club Fist Uppercut [Tag]</t>
+          <t>G-Clef - Club Fist Uppercut</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2454,6 +2454,11 @@
       <c r="N41" t="inlineStr">
         <is>
           <t>JG</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">

--- a/sources/wang_step6b.xlsx
+++ b/sources/wang_step6b.xlsx
@@ -780,6 +780,11 @@
           <t>Crouch</t>
         </is>
       </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>69bbb246-8bd8-4be1-a2c2-f1113edf6288</t>
+        </is>
+      </c>
       <c r="R7" t="inlineStr">
         <is>
           <t>69bbb246-8bd8-4be1-a2c2-f1113edf6288</t>
@@ -827,6 +832,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>b024eb39-fb8b-4f12-9207-4c48609e7fc8</t>
+        </is>
+      </c>
       <c r="R8" t="inlineStr">
         <is>
           <t>b024eb39-fb8b-4f12-9207-4c48609e7fc8</t>
@@ -879,6 +889,11 @@
           <t>TRUE</t>
         </is>
       </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>aeec6651-ae98-4599-8ef6-d5adca58c3cd</t>
+        </is>
+      </c>
       <c r="R9" t="inlineStr">
         <is>
           <t>aeec6651-ae98-4599-8ef6-d5adca58c3cd</t>
@@ -924,6 +939,11 @@
       <c r="M10" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>0bbb7217-3bd9-4aa5-bd95-cfe77d966840</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -4657,6 +4677,11 @@
       <c r="K81" t="inlineStr">
         <is>
           <t>hmmhlmhhLm</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>f2b1b105-8e73-4505-9cf6-fc48f600c675</t>
         </is>
       </c>
       <c r="R81" t="inlineStr">

--- a/sources/wang_step6b.xlsx
+++ b/sources/wang_step6b.xlsx
@@ -3775,6 +3775,11 @@
           <t>– db+4</t>
         </is>
       </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>d+4; df+4</t>
+        </is>
+      </c>
       <c r="C63" t="inlineStr">
         <is>
           <t>– Low Kick</t>
@@ -4068,6 +4073,11 @@
       <c r="A68" t="inlineStr">
         <is>
           <t>– db+4</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>d+4; df+4</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
